--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -7,13 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="분析목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="벤포드분析" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="거래처비교" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="키워드검색" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="라운드넘버" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="일자차이분析" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="벤포드이탈" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="분析목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="벤포드분析" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="거래처비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="키워드검색" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="라운드넘버" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="일자차이분析" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="심층분析" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="거래처분析" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="벤포드이탈" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,388 +434,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>분析번호</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>분析명</t>
+          <t>설정값</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ClientName</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>경남제약㈜</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>감사 대상 회사명</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>StartDate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD 형식 (당기 1분기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EndDate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD 형식</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TargetYear</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>당기 회계연도</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>임계값</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>최대건수</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>거래처비교</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>전기/당기 거래처별 금액 비교</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>벤포드분析</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>첫째자리 빈도 벤포드 기댓값 비교</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>판매촉진비</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데이터개요</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>전체 데이터 건수/금액 요약</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>계정명리스트</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>계정명 목록 및 금액 통계</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>사원별집계</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>사원별 차변/대변 계정 집계</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>일자차이분析</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>결의일자 vs 회계일자 N일 이상 차이 전표 추출</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>상대계정분析</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>특정 계정의 상대계정 분析</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>키워드검색</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>적요 키워드 검색</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>라운드넘버</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>특정 배수 단위 금액 탐지</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>특수관계자분析</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>특수관계자 거래처 필터링</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>자산부채교차</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>자산/부채 동시 발생 거래처</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>매출비용교차</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>매출/비용 동시 발생 거래처</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>심층분析</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>계정별 거래처 Top N 추출</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>AI계정별분析</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>계정별 월별 추이 및 샘플 추출</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>헤더확인</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>컬럼 인식 현황 점검</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>거래처분析</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>특정 거래처 상세 및 월별 집계</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>벤포드이탈</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>벤포드 이탈 전표 상세 추출</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>월별전계정분析</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>전 계정 월별 차변/대변 집계</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
         </is>
       </c>
     </row>
@@ -827,91 +663,388 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>분析번호</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>금액열</t>
+          <t>분析명</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>설명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>접대비</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>거래처비교</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>복리후생비</t>
-        </is>
+      <c r="A3" t="n">
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>벤포드분析</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>여비교통비</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>데이터개요</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>판매관리비</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>계정명리스트</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>사원별집계</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>일자차이분析</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>결의일자 vs 회계일자 N일 이상 지연 전표 → 일자차이분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>상대계정분析</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>특정 계정의 상대계정 분析 → 상대계정분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>키워드검색</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>라운드넘버</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>특수관계자분析</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>특수관계자 거래처 필터링 → 특수관계자분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>자산부채교차</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>자산/부채 동시 발생 거래처 분析</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>매출비용교차</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>매출/비용 동시 발생 거래처 분析</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>심층분析</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>계정별 거래처 Top N 추출 → 심층분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AI계정별분析</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>헤더확인</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>거래처분析</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>특정 거래처 복합조건 상세 분析 → 거래처분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>벤포드이탈</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월별전계정분析</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -926,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +1078,11 @@
           <t>실행여부</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -962,6 +1100,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>판관비 중 현금성 지출 — 이상패턴 탐지 핵심</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -979,6 +1122,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>인원 대비 과다 지출 여부 확인</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -993,7 +1141,56 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>기말 집중 계상 여부 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>판매촉진비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>리베이트성 지출 가능성</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>전체 계정 — 데이터 많을 경우 느릴 수 있음</t>
         </is>
       </c>
     </row>
@@ -1008,126 +1205,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>키워드</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>상품권</t>
+          <t>접대비</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>전기 대비 거래처별 증감 확인</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>접대</t>
+          <t>복리후생비</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>전기 대비 거래처별 증감 확인</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>가수금</t>
+          <t>여비교통비</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>선물</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>회식</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>결산수정</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>가지급</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>리베이트</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>현금</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>필요시 활성화</t>
         </is>
       </c>
     </row>
@@ -1142,68 +1307,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>키워드</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>금액열</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>최소금액</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(전체)</t>
+          <t>상품권</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>현금성 접대 탐지</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(전체)</t>
+          <t>접대</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>접대비 관련 적요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>가수금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>비공식 자금 흐름</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>선물</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>현금성 접대 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>회식</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>복리후생/접대 경계</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>결산수정</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기말 조정 분개</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>가지급</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>미정산 선지출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>리베이트</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>제약업 판촉비 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>현금</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>현금 직접 지출</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>샘플</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>제약 샘플 비용 (판촉/접대 경계)</t>
         </is>
       </c>
     </row>
@@ -1218,28 +1508,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>기준일수</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>최소금액</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10만원 이상 라운드 수 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10만원 이상 라운드 수 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>접대비 50만원 단위 집중 확인 시 활성화</t>
         </is>
       </c>
     </row>
@@ -1254,33 +1624,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>기준일수</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>결의일자 대비 회계일자 7일 이상 지연 전표</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>계정과목</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>개수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>임계값</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>최대건수</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>실행여부</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1290,20 +1706,22 @@
           <t>접대비</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D2" t="n">
-        <v>200</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>거래처별 Top 20 — 리베이트성 지출 탐지</t>
         </is>
       </c>
     </row>
@@ -1313,20 +1731,198 @@
           <t>복리후생비</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>거래처별 Top 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>판매촉진비</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>거래처별 Top 20 — 제약 리베이트 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>여비교통비</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>필요시 활성화</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>고액거래처_접대비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>거래처 확정 후 거래처명 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>고액거래처_판촉비</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>판매촉진비</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D3" t="n">
-        <v>200</v>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>거래처 확정 후 거래처명 입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>특수관계자_매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>거래처명 확정 후 입력</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="분析목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="벤포드분析" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="벤포드분석" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="거래처비교" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="키워드검색" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="라운드넘버" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="일자차이분析" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="심층분析" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="거래처분析" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="일자차이분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="심층분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="거래처분석" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="벤포드이탈" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,7 +674,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>분析명</t>
+          <t>분석명</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -685,6 +685,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>분析대상</t>
         </is>
       </c>
     </row>
@@ -707,6 +712,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -714,17 +724,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>벤포드분析</t>
+          <t>벤포드분석</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분析 시트 참조</t>
+          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -747,6 +762,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -767,6 +787,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -787,6 +812,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -794,17 +824,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>일자차이분析</t>
+          <t>일자차이분석</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>결의일자 vs 회계일자 N일 이상 지연 전표 → 일자차이분析 시트 참조</t>
+          <t>결의일자 vs 회계일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -814,17 +849,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>상대계정분析</t>
+          <t>상대계정분석</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>특정 계정의 상대계정 분析 → 상대계정분析 시트 참조</t>
+          <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -847,6 +887,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -867,6 +912,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -874,17 +924,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>특수관계자분析</t>
+          <t>특수관계자분석</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>특수관계자 거래처 필터링 → 특수관계자분析 시트 참조</t>
+          <t>특수관계자 거래처 필터링 → 특수관계자분석 시트 참조</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -899,12 +954,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>자산/부채 동시 발생 거래처 분析</t>
+          <t>자산/부채 동시 발생 거래처 분석</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -919,12 +979,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>매출/비용 동시 발생 거래처 분析</t>
+          <t>매출/비용 동시 발생 거래처 분석</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -934,17 +999,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>심층분析</t>
+          <t>심층분석</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>계정별 거래처 Top N 추출 → 심층분析 시트 참조</t>
+          <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -954,17 +1024,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI계정별분析</t>
+          <t>AI계정별분석</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분析 시트 참조</t>
+          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -987,6 +1062,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -994,17 +1074,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>거래처분析</t>
+          <t>거래처분석</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>특정 거래처 복합조건 상세 분析 → 거래처분析 시트 참조</t>
+          <t>특정 거래처 복합조건 상세 분석 → 거래처분서 시트 참조</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -1027,6 +1112,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1034,7 +1124,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>월별전계정분析</t>
+          <t>월별전계정분석</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1045,6 +1135,11 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>전체</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,25 +16,37 @@
     <sheet name="심층분석" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="거래처분석" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="벤포드이탈" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="특수관계자" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,10 +66,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -71,7 +91,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -435,7 +455,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -534,121 +554,168 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>임계값</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>최대건수</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>판매촉진비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>임계값 3%p 이상 이탈 건 추출</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>임계값</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>최대건수</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>접대비</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D2" t="n">
-        <v>200</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>임계값 3%p 이상 이탈 건 추출</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>복리후생비</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D3" t="n">
-        <v>200</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>임계값 3%p 이상 이탈 건 추출</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>판매촉진비</t>
-        </is>
-      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D4" t="n">
-        <v>200</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>임계값 3%p 이상 이탈 건 추출</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -664,7 +731,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="15.25" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -934,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1225,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1301,7 +1371,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1403,7 +1473,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1604,7 +1674,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1720,7 +1790,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1766,7 +1836,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1907,7 +1977,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1952,7 +2022,6 @@
           <t>접대비</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>차변</t>
@@ -1980,7 +2049,6 @@
           <t>판매촉진비</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>차변</t>
@@ -2003,8 +2071,6 @@
           <t>특수관계자_매출</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>대변</t>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -1,30 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\journal_analyzer\kyungnam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2885280C-D7C2-4A3D-B261-DE131FC4E9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE6A81B-3A3F-4FE3-AA37-B687E20FD20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{F61C05E1-67E3-4811-9CCA-55C28B2BAB60}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" r:id="rId2"/>
-    <sheet name="벤포드 분석" sheetId="3" r:id="rId3"/>
-    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId4"/>
-    <sheet name="특수관계자 분석" sheetId="5" r:id="rId5"/>
+    <sheet name="심층분석 (계정별 Top) " sheetId="6" r:id="rId3"/>
+    <sheet name="총계정원장" sheetId="7" r:id="rId4"/>
+    <sheet name="거래처 전기_당기 비교" sheetId="8" r:id="rId5"/>
+    <sheet name="상대계정 분석" sheetId="13" r:id="rId6"/>
+    <sheet name="벤포드 분석" sheetId="3" r:id="rId7"/>
+    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId8"/>
+    <sheet name="매출 vs 비용 교차" sheetId="9" r:id="rId9"/>
+    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="10" r:id="rId10"/>
+    <sheet name="계정별 상세거래내역" sheetId="12" r:id="rId11"/>
+    <sheet name="특수관계자 분석" sheetId="11" r:id="rId12"/>
+    <sheet name="리스완전성" sheetId="14" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="202">
   <si>
     <t>분석번호</t>
   </si>
@@ -41,9 +62,6 @@
     <t>분석대상</t>
   </si>
   <si>
-    <t>거래처 전기/당기 비교</t>
-  </si>
-  <si>
     <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
   </si>
   <si>
@@ -206,9 +224,6 @@
     <t>보통예금</t>
   </si>
   <si>
-    <t>O</t>
-  </si>
-  <si>
     <t>(전체)</t>
   </si>
   <si>
@@ -218,13 +233,473 @@
     <t>최소금액</t>
   </si>
   <si>
-    <t>10만원 이상 라운드 수 탐지</t>
-  </si>
-  <si>
-    <t>보통예금만 50만원 기준 (선택)</t>
-  </si>
-  <si>
     <t>㈜경남제약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처 전기_당기 비교</t>
+  </si>
+  <si>
+    <t>잔액증감분석 (계정별 거래처별)</t>
+  </si>
+  <si>
+    <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
+  </si>
+  <si>
+    <t>총계정원장</t>
+  </si>
+  <si>
+    <t>전기/당기/전당기 기간의 게정별 월별합계 차/대/전체로 추출</t>
+  </si>
+  <si>
+    <t>은행조회서 완전성</t>
+  </si>
+  <si>
+    <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
+  </si>
+  <si>
+    <t>계정과목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기금융상품_MMF</t>
+  </si>
+  <si>
+    <t>단기금융상품_정기예금</t>
+  </si>
+  <si>
+    <t>미지급금(거래처)</t>
+  </si>
+  <si>
+    <t>미지급금(사원)</t>
+  </si>
+  <si>
+    <t>미지급비용(급여)</t>
+  </si>
+  <si>
+    <t>미지급비용(신용카드)</t>
+  </si>
+  <si>
+    <t>미지급비용(이자)</t>
+  </si>
+  <si>
+    <t>외주가공비(제조)</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>자산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>투자부동산_건물</t>
+  </si>
+  <si>
+    <t>투자부동산_건물감가상각누계액</t>
+  </si>
+  <si>
+    <t>투자부동산_건설중인자산</t>
+  </si>
+  <si>
+    <t>투자부동산_토지</t>
+  </si>
+  <si>
+    <t>건물</t>
+  </si>
+  <si>
+    <t>건물감가상각누계액</t>
+  </si>
+  <si>
+    <t>건설중인자산</t>
+  </si>
+  <si>
+    <t>구축물감가상각누계액</t>
+  </si>
+  <si>
+    <t>기계장치감가상각누계액</t>
+  </si>
+  <si>
+    <t>비품감가상각누계액</t>
+  </si>
+  <si>
+    <t>사용권자산</t>
+  </si>
+  <si>
+    <t>사용권자산감가상각누계액</t>
+  </si>
+  <si>
+    <t>시설장치</t>
+  </si>
+  <si>
+    <t>시설장치감가상각누계액</t>
+  </si>
+  <si>
+    <t>차량운반구</t>
+  </si>
+  <si>
+    <t>차량운반구감가상각누계액</t>
+  </si>
+  <si>
+    <t>구축물</t>
+  </si>
+  <si>
+    <t>구축물</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계장치</t>
+  </si>
+  <si>
+    <t>기계장치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비품</t>
+  </si>
+  <si>
+    <t>비품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타의무형자산</t>
+  </si>
+  <si>
+    <t>보증금_임차보증금</t>
+  </si>
+  <si>
+    <t>보증금_임차보증금(현재가치할인차금)</t>
+  </si>
+  <si>
+    <t>임대보증금</t>
+  </si>
+  <si>
+    <t>예수금_갑근소득세</t>
+  </si>
+  <si>
+    <t>예수금_갑근주민세</t>
+  </si>
+  <si>
+    <t>예수금_건강보험</t>
+  </si>
+  <si>
+    <t>예수금_고용보험</t>
+  </si>
+  <si>
+    <t>예수금_국민연금</t>
+  </si>
+  <si>
+    <t>예수금_기타</t>
+  </si>
+  <si>
+    <t>예수금_부가세</t>
+  </si>
+  <si>
+    <t>예수부가세(세금계산서)</t>
+  </si>
+  <si>
+    <t>예수부가세(수입금액제외)</t>
+  </si>
+  <si>
+    <t>일반선수금</t>
+  </si>
+  <si>
+    <t>장기미지급비용</t>
+  </si>
+  <si>
+    <t>부채</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴직급여(제조)</t>
+  </si>
+  <si>
+    <t>퇴직급여(판관)</t>
+  </si>
+  <si>
+    <t>퇴직급여충당금</t>
+  </si>
+  <si>
+    <t>퇴직연금예치금</t>
+  </si>
+  <si>
+    <t>비용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품매출_국내</t>
+  </si>
+  <si>
+    <t>제품매출(외주)_국내</t>
+  </si>
+  <si>
+    <t>제품매출(자사)_국내</t>
+  </si>
+  <si>
+    <t>선급금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10억원 이상 라운드 수 탐지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금만 5억원 기준 (선택)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제예금(보통예금)</t>
+  </si>
+  <si>
+    <t>접대비_거래처(판관)</t>
+  </si>
+  <si>
+    <t>접대비_경조금(판관)</t>
+  </si>
+  <si>
+    <t>접대비_관계처(제조)</t>
+  </si>
+  <si>
+    <t>접대비_관계처(판관)</t>
+  </si>
+  <si>
+    <t>접대비_상품권(판관)</t>
+  </si>
+  <si>
+    <t>접대비_선물대(판관)</t>
+  </si>
+  <si>
+    <t>지급수수료_기타지급수수료(판관)</t>
+  </si>
+  <si>
+    <t>지급수수료_신용카드(판관)</t>
+  </si>
+  <si>
+    <t>지급수수료_용역료(제조)</t>
+  </si>
+  <si>
+    <t>㈜판타지오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>키위제1호조합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜아센디오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>솔리드원투자조합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이리스투자조합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터솔루션</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이치월드와이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜하나모두</t>
+  </si>
+  <si>
+    <t>㈜아티스트</t>
+  </si>
+  <si>
+    <t>㈜온누리투어</t>
+  </si>
+  <si>
+    <t>㈜온누리프로덕션</t>
+  </si>
+  <si>
+    <t>㈜온누리파트너스</t>
+  </si>
+  <si>
+    <t>㈜온누리미디어</t>
+  </si>
+  <si>
+    <t>㈜남산물산</t>
+  </si>
+  <si>
+    <t>㈜남산홀딩스</t>
+  </si>
+  <si>
+    <t>㈜마코컴퍼니</t>
+  </si>
+  <si>
+    <t>㈜스튜디오파니니</t>
+  </si>
+  <si>
+    <t>판타지오 홍콩(Fantagio Hong Kong Co., Ltd.)</t>
+  </si>
+  <si>
+    <t>㈜엑스</t>
+  </si>
+  <si>
+    <t>METAGIO PTE.LTD.</t>
+  </si>
+  <si>
+    <t>HUMASIS VINACompany Limited</t>
+  </si>
+  <si>
+    <t>(유)플랜에스문화산업전문회사</t>
+  </si>
+  <si>
+    <t>(유)드림사이드문화산업전문회사</t>
+  </si>
+  <si>
+    <t>(유)의녀대장금문화산업전문회사</t>
+  </si>
+  <si>
+    <t>㈜빌리언스플러스</t>
+  </si>
+  <si>
+    <t>㈜엑스와이지스튜디오</t>
+  </si>
+  <si>
+    <t>HUMASIS
+MINE SOLUTIONS LIMITED</t>
+  </si>
+  <si>
+    <t>㈜판타지오엠</t>
+  </si>
+  <si>
+    <t>휴마시스㈜</t>
+  </si>
+  <si>
+    <t>김성곤</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>남궁정</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>신민규</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>조정영</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정별 상세거래내역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 계정별로 계정과목 차변/대변/차변대변모두 를 선택하여 데어터추출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금액유형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>실행여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사용권자산 </t>
+  </si>
+  <si>
+    <t>외상매출금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>외상매출금 상대계정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수금 상대계정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금 상대계정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지급금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지급금 상대계정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>제품매출 상대게정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹기준열</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회계번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리스완전성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-IFRS 116호 리스 인식 대상 완정성 검토</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임차료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급수수료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차량유지비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물관리비</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -232,7 +707,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +732,28 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -303,10 +803,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -323,17 +826,30 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -644,38 +1160,38 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4">
         <v>46023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5">
         <v>46387</v>
@@ -684,7 +1200,7 @@
     </row>
     <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>2026</v>
@@ -697,14 +1213,756 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C32EF0D-7780-4EC6-AA98-FCE4EE834F7C}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="30.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1381568B-71B1-4CA2-8D93-4F320ACA89C2}">
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D271B8-CC89-4CEE-9877-9C89B1A8F01E}">
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B92AE9-6324-4D6C-A91B-C1147E4DDBF2}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -726,309 +1984,394 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="6">
+      <c r="A2" s="12">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="12">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="12">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="12">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="7">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="7">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="6">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="7">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="7">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="7">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="6">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="7">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="7">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="7">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="8">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="7">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="7">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="8">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="7">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="7">
         <v>24</v>
       </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="8">
+      <c r="B24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
         <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="8">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="8">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="8">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="8">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="8">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="8">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="8">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" s="8">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="8">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1038,8 +2381,696 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3330A546-AD13-4B19-B667-401C36BA572B}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418C6F31-83A6-489D-85C9-168A52085EE0}">
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="28.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19510F6-0EAE-469B-BF83-29369127DBD1}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C9" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11927642-93ED-4BF9-A47A-382661C782B6}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1050,78 +3081,138 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="B5" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+      <c r="C5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +3221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1144,68 +3235,68 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2">
-        <v>100000</v>
+        <v>55</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1000000000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="3">
-        <v>100000</v>
+        <v>57</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1000000000</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2">
-        <v>500000</v>
+        <v>55</v>
+      </c>
+      <c r="C4" s="9">
+        <v>500000000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1214,36 +3305,120 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B4"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4B87AF1-13FB-4835-87D4-C83DB3939BBE}">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="25.4140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1">
-        <v>11</v>
+      <c r="A1" t="s">
+        <v>133</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\journal_analyzer\kyungnam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE6A81B-3A3F-4FE3-AA37-B687E20FD20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E381750B-075B-48C5-8FB6-BB9FF326868E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{F61C05E1-67E3-4811-9CCA-55C28B2BAB60}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" firstSheet="1" activeTab="1" xr2:uid="{F61C05E1-67E3-4811-9CCA-55C28B2BAB60}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="214">
   <si>
     <t>분석번호</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>실행여부</t>
-  </si>
-  <si>
-    <t>분석대상</t>
   </si>
   <si>
     <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
@@ -700,6 +697,50 @@
   </si>
   <si>
     <t>건물관리비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>급료와임금_급여(판관)</t>
+  </si>
+  <si>
+    <t>급료와임금_연차수당(판관)</t>
+  </si>
+  <si>
+    <t>급여 급료 (제조)</t>
+  </si>
+  <si>
+    <t>급여 급료(제조)의령</t>
+  </si>
+  <si>
+    <t>급여_기타(제조)</t>
+  </si>
+  <si>
+    <t>급여_연월차(제조)</t>
+  </si>
+  <si>
+    <t>상여금(제조)</t>
+  </si>
+  <si>
+    <t>상여금_인센티브(판관)</t>
+  </si>
+  <si>
+    <t>퇴직연금예치금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기미지급비용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>임대보증금(비유동)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기준월</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분석대상</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -779,7 +820,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -802,6 +843,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -809,7 +859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -845,6 +895,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,38 +1213,38 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4">
         <v>46023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="5">
         <v>46387</v>
@@ -1200,7 +1253,7 @@
     </row>
     <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <v>2026</v>
@@ -1223,154 +1276,154 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1381,231 +1434,451 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1381568B-71B1-4CA2-8D93-4F320ACA89C2}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" t="s">
         <v>182</v>
-      </c>
-      <c r="C1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
         <v>125</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>63</v>
+      <c r="C28" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1624,7 +1897,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -1632,266 +1905,266 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1911,42 +2184,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1966,7 +2239,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1979,263 +2252,269 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E1" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="12">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="12">
         <v>3</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="12">
         <v>4</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="12">
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="12">
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>9</v>
       </c>
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>10</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
       <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
         <v>6</v>
       </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="7">
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="7">
         <v>14</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="7">
         <v>15</v>
       </c>
       <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="7">
         <v>16</v>
       </c>
       <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
       <c r="D16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -2243,16 +2522,16 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -2260,16 +2539,16 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -2277,16 +2556,16 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -2294,16 +2573,16 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
         <v>65</v>
       </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -2311,16 +2590,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
         <v>67</v>
       </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -2328,16 +2607,16 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
         <v>69</v>
       </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
@@ -2345,16 +2624,16 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" t="s">
         <v>180</v>
       </c>
-      <c r="C23" t="s">
-        <v>181</v>
-      </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
@@ -2362,16 +2641,16 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" t="s">
         <v>196</v>
       </c>
-      <c r="C24" t="s">
-        <v>197</v>
-      </c>
       <c r="D24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2390,57 +2669,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2451,7 +2730,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418C6F31-83A6-489D-85C9-168A52085EE0}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="28.9140625" bestFit="1" customWidth="1"/>
@@ -2459,386 +2738,450 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" t="s">
         <v>81</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2859,60 +3202,60 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -2945,121 +3288,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
         <v>186</v>
-      </c>
-      <c r="B2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" t="s">
         <v>188</v>
-      </c>
-      <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" t="s">
         <v>191</v>
-      </c>
-      <c r="B5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -3081,138 +3424,138 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="C2" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="C5" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3235,68 +3578,68 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="9">
         <v>1000000000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="10">
         <v>1000000000</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="9">
         <v>500000000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3315,106 +3658,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -20,6 +20,8 @@
     <sheet name="특수관계자 분석" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="손익항목분析" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -31,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -76,8 +78,30 @@
       <sz val="10"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +123,28 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -132,6 +176,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -139,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,6 +243,24 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2163,13 +2239,359 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>분析01</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr"/>
+      <c r="C3" s="18" t="inlineStr"/>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>분析02</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr"/>
+      <c r="C4" s="18" t="inlineStr"/>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>분析03</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr"/>
+      <c r="C5" s="18" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>분析04</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr"/>
+      <c r="C6" s="18" t="inlineStr"/>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>분析05</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr"/>
+      <c r="C7" s="18" t="inlineStr"/>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr"/>
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="19" t="inlineStr"/>
+      <c r="E8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr"/>
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="19" t="inlineStr"/>
+      <c r="E11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr"/>
+      <c r="D12" s="19" t="inlineStr"/>
+      <c r="E12" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>판매비와관리비</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>영업외수익</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2785,6 +3207,31 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>손익항목분析</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>손익 계정별 전기/당기 차변·대변 선택 비교 (월별 + 거래처별)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>전체</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -21,7 +21,7 @@
     <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익항목분析" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손익항목분析</t>
+          <t>손익월별분析</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -22,6 +22,7 @@
     <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -197,7 +198,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -262,6 +263,7 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2585,13 +2587,55 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3234,6 +3278,33 @@
           <t>전체</t>
         </is>
       </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -23,6 +23,7 @@
     <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2629,13 +2630,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외화환산손익</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융자산평가손익</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>대손상각비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파생상품평가손익</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3279,7 +3438,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="22" t="n">
         <v>26</v>
@@ -3305,6 +3463,32 @@
         </is>
       </c>
       <c r="F27" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>감가상각_평가손익분석</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -24,6 +24,7 @@
     <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2788,6 +2789,258 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>유형자산계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>감가상각누계액계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>건물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>구축물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기계장치감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차량운반구감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>시설장치감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>비품감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>사용권자산감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>투자부동산_건물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -2795,7 +2795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2817,10 +2817,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>대체상대계정</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>취득원가_수동조정</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상각누계액_수동조정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2832,12 +2847,12 @@
           <t>토지</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2856,10 +2871,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>건설중인자산,투자부동산_건물</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2876,12 +2896,12 @@
           <t>구축물감가상각누계액</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2898,12 +2918,12 @@
           <t>기계장치감가상각누계액</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2920,12 +2940,12 @@
           <t>차량운반구감가상각누계액</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2942,12 +2962,12 @@
           <t>시설장치감가상각누계액</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2964,12 +2984,12 @@
           <t>비품감가상각누계액</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -2983,12 +3003,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11) / 26년에는 건물로의 완성대체 금액 없음(대체상대계정은 향후 대비 유지, 2026-08-12)</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3028,12 @@
           <t>사용권자산감가상각누계액</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
         </is>
@@ -3027,12 +3052,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>건물,투자부동산_건설중인자산</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>실제 kyungnam 분개장 계정명 기준으로 확인된 조합 (2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>투자부동산_건설중인자산</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>건물/투자부동산_건물 대체 검증 중 발견된 계정 (2026-08-12 추가)</t>
         </is>
       </c>
     </row>
@@ -3691,6 +3743,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="22" t="n">
         <v>26</v>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -25,6 +25,7 @@
     <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3801,6 +3802,64 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>처분이익계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>처분손실계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유형자산처분이익</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>유형자산처분손실</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>실제 kyungnam 계정과목 확인됨 (2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="9" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -37,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -70,13 +70,6 @@
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
       <family val="3"/>
       <color theme="1"/>
       <sz val="10"/>
@@ -84,24 +77,32 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <i val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="FF7F6000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <i val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="FF375623"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -129,22 +130,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
+        <fgColor rgb="FF70AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,17 +183,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -201,7 +203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -233,7 +235,7 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,31 +244,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -636,12 +639,12 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" style="20" min="1" max="1"/>
+    <col width="22" customWidth="1" style="20" min="2" max="2"/>
+    <col width="30" customWidth="1" style="20" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -658,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="20">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -671,7 +674,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="20">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -686,7 +689,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="20">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -697,7 +700,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="16" customHeight="1" s="20">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -722,7 +725,7 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="30.58203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -967,8 +970,8 @@
   <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="34.08203125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="34.08203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1665,7 +1668,7 @@
   <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="40.9140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="40.9140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2091,8 +2094,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="10.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.58203125" customWidth="1" style="20" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2166,8 +2169,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="20.25" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2236,6 +2242,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>유동성전환상환우선주</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fzj</t>
         </is>
       </c>
     </row>
@@ -2247,183 +2260,182 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00ED7D31"/>
+    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" style="20" min="1" max="1"/>
+    <col width="25" customWidth="1" style="20" min="2" max="2"/>
+    <col width="35" customWidth="1" style="20" min="3" max="3"/>
+    <col width="10" customWidth="1" style="20" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="20">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="20">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>작업명</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>거래처명</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="20">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>분析01</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr"/>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="20">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>분析02</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr"/>
-      <c r="C4" s="18" t="inlineStr"/>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="20">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>분析03</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr"/>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="20">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>분析04</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr"/>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="E6" s="19" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="20">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>분析05</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr"/>
-      <c r="C7" s="18" t="inlineStr"/>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="18" t="inlineStr"/>
-      <c r="C8" s="18" t="inlineStr"/>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="18" t="inlineStr"/>
-      <c r="C10" s="18" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="18" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="19" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr"/>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="18" t="inlineStr"/>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="19" t="inlineStr"/>
+    <row r="8" ht="18" customHeight="1" s="20">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="20">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="20">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="20">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="20">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2436,151 +2448,180 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="FF70AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" style="20" min="1" max="1"/>
+    <col width="10" customWidth="1" style="20" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="20">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="20">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>손익구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="20">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="20">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>매출원가</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="20">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>판매비와관리비</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>판관비</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="20">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>영업외수익</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>영업외수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="20">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>영업외비용</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>차변</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr"/>
-      <c r="C8" s="19" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="18" t="inlineStr"/>
-      <c r="B9" s="19" t="inlineStr"/>
-      <c r="C9" s="19" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr"/>
-      <c r="B10" s="19" t="inlineStr"/>
-      <c r="C10" s="19" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="18" t="inlineStr"/>
-      <c r="B11" s="19" t="inlineStr"/>
-      <c r="C11" s="19" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr"/>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="19" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>영업외비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="20">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="20">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="20">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="20">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="20">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2597,10 +2638,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" style="20" min="1" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2639,13 +2679,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" style="20" min="1" max="1"/>
+    <col width="10" customWidth="1" style="20" min="2" max="2"/>
+    <col width="12" customWidth="1" style="20" min="3" max="3"/>
+    <col width="10" customWidth="1" style="20" min="4" max="4"/>
+    <col width="55" customWidth="1" style="20" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2797,12 +2837,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" style="20" min="1" max="1"/>
+    <col width="26" customWidth="1" style="20" min="2" max="2"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
+    <col width="55" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3103,13 +3143,13 @@
   <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="20" min="1" max="1"/>
+    <col width="28.83203125" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
+    <col width="72.5" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
+    <col width="12" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -3141,7 +3181,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="20">
       <c r="A2" s="12" t="n">
         <v>2</v>
       </c>
@@ -3169,7 +3209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="20">
       <c r="A3" s="12" t="n">
         <v>3</v>
       </c>
@@ -3194,7 +3234,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="20">
       <c r="A4" s="12" t="n">
         <v>4</v>
       </c>
@@ -3219,7 +3259,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="16" customHeight="1" s="20">
       <c r="A5" s="12" t="n">
         <v>5</v>
       </c>
@@ -3244,7 +3284,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="16" customHeight="1" s="20">
       <c r="A6" s="12" t="n">
         <v>6</v>
       </c>
@@ -3269,7 +3309,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="16" customHeight="1" s="20">
       <c r="A7" s="6" t="n">
         <v>7</v>
       </c>
@@ -3744,58 +3784,57 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
-      <c r="A27" s="22" t="n">
+      <c r="A27" s="18" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>AI계정별분석_실행</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>당기</t>
         </is>
       </c>
-      <c r="F27" s="22" t="n"/>
+      <c r="F27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n">
+      <c r="A28" s="18" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>감가상각_평가손익분석</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>당기</t>
         </is>
       </c>
-      <c r="F28" s="22" t="n"/>
+      <c r="F28" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3809,7 +3848,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="16.25" bestFit="1" customWidth="1" style="20" min="1" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3847,11 +3889,6 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>실제 kyungnam 계정과목 확인됨 (2026-08-12)</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3906,7 @@
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3963,7 +4000,7 @@
   <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="28.9140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="28.9140625" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4652,12 +4689,12 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.33203125" customWidth="1" min="2" max="2"/>
-    <col width="15.75" customWidth="1" min="3" max="3"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+    <col width="14.33203125" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15.75" customWidth="1" style="20" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -4773,9 +4810,9 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="9.5" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="17" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
+    <col width="17" bestFit="1" customWidth="1" style="20" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4981,13 +5018,13 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" style="20" min="1" max="1"/>
+    <col width="10" customWidth="1" style="20" min="2" max="2"/>
+    <col width="12" customWidth="1" style="20" min="3" max="3"/>
+    <col width="42" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -5009,7 +5046,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="20">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>외상매출금</t>
@@ -5027,7 +5064,7 @@
       </c>
       <c r="D2" s="8" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="20">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>선급금</t>
@@ -5045,7 +5082,7 @@
       </c>
       <c r="D3" s="8" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="20">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>외주가공비(제조)</t>
@@ -5063,7 +5100,7 @@
       </c>
       <c r="D4" s="8" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="16" customHeight="1" s="20">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>외상매입금</t>
@@ -5081,7 +5118,7 @@
       </c>
       <c r="D5" s="8" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="16" customHeight="1" s="20">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>제예금(보통예금)</t>
@@ -5099,7 +5136,7 @@
       </c>
       <c r="D6" s="8" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="16" customHeight="1" s="20">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>제예금(보통예금)</t>
@@ -5117,7 +5154,7 @@
       </c>
       <c r="D7" s="8" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="16" customHeight="1" s="20">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>상품매출_국내</t>
@@ -5135,7 +5172,7 @@
       </c>
       <c r="D8" s="8" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="16" customHeight="1" s="20">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>제품매출(외주)_국내</t>
@@ -5153,7 +5190,7 @@
       </c>
       <c r="D9" s="8" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="16" customHeight="1" s="20">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>제품매출(자사)_국내</t>
@@ -5171,7 +5208,7 @@
       </c>
       <c r="D10" s="8" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="16" customHeight="1" s="20">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -5207,14 +5244,14 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" style="20" min="1" max="1"/>
+    <col width="10" customWidth="1" style="20" min="2" max="2"/>
+    <col width="14" customWidth="1" style="20" min="3" max="3"/>
+    <col width="12" customWidth="1" style="20" min="4" max="4"/>
+    <col width="36" customWidth="1" style="20" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -5241,7 +5278,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="16" customHeight="1" s="20">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -5252,7 +5289,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="22" t="n">
         <v>1000000000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5266,7 +5303,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="16" customHeight="1" s="20">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -5277,7 +5314,7 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="23" t="n">
         <v>1000000000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -5287,7 +5324,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="16" customHeight="1" s="20">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>보통예금</t>
@@ -5298,7 +5335,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="22" t="n">
         <v>500000000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -5326,7 +5363,7 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
+++ b/journal_analyzer/kyungnam/task_list_kyungnam.xlsx
@@ -8,22 +8,22 @@
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="총계정원장" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="상대계정 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="벤포드 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="라운드넘버 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="계정별 상세거래내역" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="특수관계자 분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="리스완전성" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="거래처분析" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="02_거래처 전기_당기 비교" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_벤포드 분석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="08_상대계정 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="10_라운드넘버 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="11_특수관계자 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="13_매출 vs 비용 교차" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="14_심층분석 (계정별 Top) " sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="17_거래처분석" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="21_총계정원장" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="22_은행조회서 완전성" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="23_계정별 상세거래내역" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="24_리스완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="25_손익월별분析" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
@@ -719,1547 +719,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금(현재가치할인차금)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>임대보증금</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미지급금(사원)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>미지급금(거래처)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>미지급비용(급여)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>미지급비용(이자)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>미지급비용(신용카드)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>예수금_갑근소득세</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>예수금_갑근주민세</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>예수금_건강보험</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>예수금_고용보험</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>예수금_국민연금</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>예수금_기타</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>예수금_부가세</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>예수부가세(세금계산서)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>예수부가세(수입금액제외)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>일반선수금</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="34.08203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>금액유형</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>투자부동산_토지</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>투자부동산_건물</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>투자부동산_건설중인자산</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>투자부동산_토지</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>투자부동산_건물</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>투자부동산_건설중인자산</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>토지</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>건물</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>구축물</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>기계장치</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>차량운반구</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>비품</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>시설장치</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>건설중인자산</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용권자산 </t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>기타의무형자산</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>토지</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>건물</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>구축물</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>기계장치</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>차량운반구</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>비품</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>시설장치</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>건설중인자산</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용권자산 </t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>기타의무형자산</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금(현재가치할인차금)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>임대보증금</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>임대보증금</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>퇴직연금예치금</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>퇴직연금예치금</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>장기미지급비용</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>장기미지급비용</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>임대보증금(비유동)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>임대보증금(비유동)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="40.9140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>㈜판타지오</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>키위제1호조합</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>㈜아센디오</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>솔리드원투자조합</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>이리스투자조합</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>데이터솔루션</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>에이치월드와이드</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>㈜하나모두</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>㈜아티스트</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>㈜온누리투어</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>㈜온누리프로덕션</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>㈜온누리파트너스</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>㈜온누리미디어</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>㈜남산물산</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>㈜남산홀딩스</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>㈜마코컴퍼니</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>㈜스튜디오파니니</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>판타지오 홍콩(Fantagio Hong Kong Co., Ltd.)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>㈜엑스</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>METAGIO PTE.LTD.</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HUMASIS VINACompany Limited</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>(유)플랜에스문화산업전문회사</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>(유)드림사이드문화산업전문회사</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>(유)의녀대장금문화산업전문회사</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>㈜빌리언스플러스</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>㈜엑스와이지스튜디오</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>HUMASIS
-MINE SOLUTIONS LIMITED</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>㈜판타지오엠</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>휴마시스㈜</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>김성곤</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>남궁정</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>신민규</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>조정영</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="14.58203125" customWidth="1" style="20" min="1" max="1"/>
-    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>임차료</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>지급수수료</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>차량유지비</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>건물관리비</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="20.25" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>단기차입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>장기차입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>유동성장기부채</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>유동성장기차입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>전환사채</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>유동성전환사채</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>전환상환우선주</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>유동성전환상환우선주</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fzj</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2442,6 +901,1810 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="30.58203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금(현재가치할인차금)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>임대보증금</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미지급금(사원)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급금(거래처)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>미지급비용(급여)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>미지급비용(이자)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>미지급비용(신용카드)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>예수금_갑근소득세</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>예수금_갑근주민세</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>예수금_건강보험</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>예수금_고용보험</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>예수금_국민연금</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>예수금_기타</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>예수금_부가세</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>예수부가세(세금계산서)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>예수부가세(수입금액제외)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>일반선수금</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="28.9140625" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>투자부동산_건물감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>투자부동산_건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>투자부동산_토지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>건물감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>구축물감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>기계장치감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>비품감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>사용권자산감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>시설장치감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차량운반구감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>투자부동산_건물감가상각누계액</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>투자부동산_건설중인자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>투자부동산_토지</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>기타의무형자산</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금(현재가치할인차금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>임대보증금</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>미지급금(거래처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>미지급금(사원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>미지급비용(급여)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>미지급비용(신용카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>미지급비용(이자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>예수금_갑근소득세</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>예수금_갑근주민세</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>예수금_건강보험</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>예수금_고용보험</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>예수금_국민연금</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>예수금_기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>예수금_부가세</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>예수부가세(세금계산서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>예수부가세(수입금액제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>일반선수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>장기미지급비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>퇴직급여충당금</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>퇴직연금예치금</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>퇴직급여(제조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>퇴직급여(판관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>급료와임금_급여(판관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>급료와임금_연차수당(판관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>급여 급료 (제조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>급여 급료(제조)의령</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>급여_기타(제조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>급여_연월차(제조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>상여금(제조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>상여금_인센티브(판관)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="20.25" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>유동성장기부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>유동성장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>전환사채</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유동성전환사채</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>전환상환우선주</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>유동성전환상환우선주</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fzj</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="34.08203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액유형</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>투자부동산_토지</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>투자부동산_건설중인자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>투자부동산_토지</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>투자부동산_건물</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>투자부동산_건설중인자산</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용권자산 </t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>기타의무형자산</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>시설장치</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>건설중인자산</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용권자산 </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>기타의무형자산</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금(현재가치할인차금)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>보증금_임차보증금</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>임대보증금</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>임대보증금</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>퇴직급여충당금</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>퇴직급여충당금</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>퇴직연금예치금</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>퇴직연금예치금</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>장기미지급비용</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>장기미지급비용</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>임대보증금(비유동)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>임대보증금(비유동)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="14.58203125" customWidth="1" style="20" min="1" max="1"/>
+    <col width="8.5" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>임차료</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>건물관리비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3903,789 +4166,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>단기금융상품_MMF</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>단기금융상품_정기예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>미지급금(거래처)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미지급금(사원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>미지급비용(급여)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>미지급비용(신용카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>미지급비용(이자)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>외주가공비(제조)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="28.9140625" bestFit="1" customWidth="1" style="20" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>투자부동산_건물</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>투자부동산_건물감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>투자부동산_건설중인자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>투자부동산_토지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>건물</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>건물감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>건설중인자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>구축물</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>구축물감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>기계장치</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>기계장치감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>비품</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>비품감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>사용권자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>사용권자산감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>시설장치</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>시설장치감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>차량운반구</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>차량운반구감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>투자부동산_건물</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>투자부동산_건물감가상각누계액</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>투자부동산_건설중인자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>투자부동산_토지</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>기타의무형자산</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>보증금_임차보증금(현재가치할인차금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>임대보증금</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>미지급금(거래처)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>미지급금(사원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>미지급비용(급여)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>미지급비용(신용카드)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>미지급비용(이자)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>예수금_갑근소득세</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>예수금_갑근주민세</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>예수금_건강보험</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>예수금_고용보험</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>예수금_국민연금</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>예수금_기타</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>예수금_부가세</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>예수부가세(세금계산서)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>예수부가세(수입금액제외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>일반선수금</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>장기미지급비용</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>퇴직연금예치금</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>퇴직급여(제조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>퇴직급여(판관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>급료와임금_급여(판관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>급료와임금_연차수당(판관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>급여 급료 (제조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>급여 급료(제조)의령</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>급여_기타(제조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>급여_연월차(제조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>상여금(제조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>상여금_인센티브(판관)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
@@ -4801,215 +4281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="18.33203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
-    <col width="17" bestFit="1" customWidth="1" style="20" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>외상매출금 상대계정</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>미수금</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>미수금 상대계정</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>제예금(보통예금)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>보통예금 상대계정</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미지급금</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>미지급금 상대계정</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>제품매출(외주)_국내</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>제품매출 상대게정</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>제품매출(자사)_국내</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>회계번호</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>제품매출 상대게정</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5235,7 +4507,215 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+    <col width="9.5" bestFit="1" customWidth="1" style="20" min="3" max="3"/>
+    <col width="17" bestFit="1" customWidth="1" style="20" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>외상매출금 상대계정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>미수금</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>미수금 상대계정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>제예금(보통예금)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>보통예금 상대계정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미지급금</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>미지급금 상대계정</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>제품매출(외주)_국내</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>제품매출 상대게정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>제품매출(자사)_국내</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>회계번호</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>제품매출 상대게정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5354,7 +4834,433 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="40.9140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>㈜판타지오</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>키위제1호조합</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>㈜아센디오</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>솔리드원투자조합</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>이리스투자조합</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>데이터솔루션</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>에이치월드와이드</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>㈜하나모두</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>㈜아티스트</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>㈜온누리투어</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>㈜온누리프로덕션</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>㈜온누리파트너스</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>㈜온누리미디어</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>㈜남산물산</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>㈜남산홀딩스</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>㈜마코컴퍼니</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>㈜스튜디오파니니</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>판타지오 홍콩(Fantagio Hong Kong Co., Ltd.)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>㈜엑스</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>METAGIO PTE.LTD.</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HUMASIS VINACompany Limited</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>(유)플랜에스문화산업전문회사</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>(유)드림사이드문화산업전문회사</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(유)의녀대장금문화산업전문회사</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>㈜빌리언스플러스</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>㈜엑스와이지스튜디오</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HUMASIS
+MINE SOLUTIONS LIMITED</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>㈜판타지오엠</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>휴마시스㈜</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>김성곤</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>남궁정</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>신민규</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>조정영</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5525,4 +5431,98 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="20" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>단기금융상품_MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>단기금융상품_정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>미지급금(거래처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미지급금(사원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미지급비용(급여)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>미지급비용(신용카드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>미지급비용(이자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>외상매입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>외상매출금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>외주가공비(제조)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>